--- a/Data/EXCEL/Transfer/salemon/20240711/6488-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6488-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{884D3A1B-78AF-4EA5-8957-C574C76FD427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2851CFB9-580A-4DBC-BAC0-A15CCB41FFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{A26664F9-55A9-4DB7-AFC6-0BF8C1699BB2}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{A6FD191F-0E59-46E6-BBBC-B43FB598540C}"/>
   </bookViews>
   <sheets>
     <sheet name="6488-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,17 +1261,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E245D8D-EC1D-4190-92F2-30B2809C6304}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9169CFC3-7D4C-4E62-B58B-11216BE063BB}">
   <dimension ref="A1:Q247"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1380,7 +1380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1419,7 +1419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>-16.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>-20.9</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2744,7 +2744,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>-5.47</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>-6.66</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>-7.54</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>-8.6300000000000008</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>-9.18</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>-1.64</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4387,7 +4387,7 @@
         <v>-0.94</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>9.8699999999999992</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>150.80000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5659,7 +5659,7 @@
         <v>184.4</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>184.7</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>185.7</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>184.7</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>185.6</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>188.5</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>184.3</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>186.1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>190.1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>168.8</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>162.19999999999999</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6401,7 +6401,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>-1.19</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6507,7 +6507,7 @@
         <v>-3.48</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>-5.93</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>-7.44</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>-9.35</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>-9.81</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>-9.19</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>-4.21</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>-3.01</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>-2.34</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>-1.52</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>42125</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>42064</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>42005</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>41944</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>41883</v>
       </c>
@@ -7673,627 +7673,627 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A230" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A232" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A234" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A236" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A239" s="10">
         <v>42125</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A241" s="10">
         <v>42064</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A243" s="10">
         <v>42005</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A245" s="10">
         <v>41944</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A247" s="10">
         <v>41883</v>
       </c>
